--- a/ipo-analysis/companies/tonbo-imaging-india-ltd/TONBO_IMAGING_INDIA_LTD_03_Valuation.xlsx
+++ b/ipo-analysis/companies/tonbo-imaging-india-ltd/TONBO_IMAGING_INDIA_LTD_03_Valuation.xlsx
@@ -1828,9 +1828,14 @@
         </is>
       </c>
       <c r="C42" s="16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D42" s="21" t="inlineStr"/>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>0 by default; up to 1% only for a specific, cited, non-routine risk</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="19" t="inlineStr">
@@ -1879,12 +1884,12 @@
         </is>
       </c>
       <c r="C48" s="16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D48" s="21" t="inlineStr"/>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>80% where no comparable listed peers</t>
+          <t>70% where no comparable listed peers</t>
         </is>
       </c>
     </row>
@@ -1928,12 +1933,12 @@
         </is>
       </c>
       <c r="C52" s="16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D52" s="21" t="inlineStr"/>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>Size, liquidity, business-model gap - state why</t>
+          <t>0 by default; only for a clear business-model gap - state why</t>
         </is>
       </c>
     </row>
@@ -2268,17 +2273,17 @@
         <v/>
       </c>
       <c r="E72" s="16" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="F72" s="16" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="G72" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="H72" s="20" t="inlineStr">
         <is>
-          <t>EBITDA margin 26.23% / 29.65% / 28.85% FY24-26 (p. 144); Q1 FY27 -36.21% on low revenue. Bear 22% allows for price pressure in tenders; Neutral ~3-year average; Bull at the FY25 high.</t>
+          <t>EBITDA margin 26.23% / 29.65% / 28.85% FY24-26 (p. 144); Q1 FY27 is a seasonal low-revenue quarter. Neutral uses the three-year average (28.2%); Bear allows for tender price pressure; Bull holds the FY25 level.</t>
         </is>
       </c>
     </row>
@@ -2293,17 +2298,17 @@
         <v/>
       </c>
       <c r="E73" s="16" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="G73" s="16" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
-          <t>Trade NWC (inventory + receivables - trade payables) 43.2% / 64.0% / 109.7% of revenue FY24-26 (p. 87); issuer's working-capital days 152 / 280 / 517 (p. 144). Neutral assumes a partial unwind as the inventory built for FY27 orders is delivered.</t>
+          <t>Trade NWC 43.2% / 64.0% / 109.7% of revenue FY24-26 (p. 87). FY26 is inflated by orders deferred into FY27 and stock bought ahead of them (pp. 23, 25). Neutral uses the three-year average (about 70%); high working capital is normal for Indian defence electronics (Data Patterns: 365-432 working-capital days, p. 147). Bull returns to the FY24 level; Bear keeps most of the FY26 build.</t>
         </is>
       </c>
     </row>
@@ -2318,17 +2323,17 @@
         <v/>
       </c>
       <c r="E74" s="16" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="F74" s="16" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="G74" s="16" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="H74" s="20" t="inlineStr">
         <is>
-          <t>ROCE 67.76% / 27.41% / 14.54% FY24-26 on the issuer's definition, which excludes intangibles (p. 144). Terminal ROIC set at 14% in Neutral because the purchased IP is part of invested capital.</t>
+          <t>Issuer ROCE 67.76% / 27.41% / 14.54% FY24-26 (p. 144). Neutral terminal ROIC 16%, just above the 14.2% WACC: the business has earned well above its cost of capital in two of three years.</t>
         </is>
       </c>
     </row>
@@ -4543,11 +4548,11 @@
         </is>
       </c>
       <c r="C9" s="27">
-        <f>IF(C8&lt;=0,"No multiple: FCF negative - price rests on a turn not yet begun",C7/C8)</f>
+        <f>IF(C8&lt;=0,"No multiple: FCF negative - the price assumes cash generation improves",C7/C8)</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>IF(D8&lt;=0,"No multiple: FCF negative - price rests on a turn not yet begun",D7/D8)</f>
+        <f>IF(D8&lt;=0,"No multiple: FCF negative - the price assumes cash generation improves",D7/D8)</f>
         <v/>
       </c>
     </row>
@@ -4654,7 +4659,7 @@
         </is>
       </c>
       <c r="C16" s="12">
-        <f>IF(D8&lt;=0,"Current free cash flow is negative: no multiple can be stated, and the entire price rests on a turn that has not yet begun.","The price asks the business to deliver "&amp;TEXT(D9,"0.0")&amp;" times its current free cash flow, in perpetuity.")</f>
+        <f>IF(D8&lt;=0,"Current free cash flow is negative, so no multiple can be stated: the price assumes cash generation improves from here.","The price asks the business to deliver "&amp;TEXT(D9,"0.0")&amp;" times its current free cash flow, in perpetuity.")</f>
         <v/>
       </c>
     </row>
